--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -627,7 +627,7 @@
         <v>Interview Scheduled</v>
       </c>
       <c r="H5" t="str">
-        <v>20-Aug-2026, 2:00 pm</v>
+        <v>22-Aug-2026, 11:00 am</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -639,16 +639,16 @@
         <v>NO</v>
       </c>
       <c r="L5" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M5" t="str">
         <v>20-Aug-2026, 2:12 pm</v>
       </c>
       <c r="N5" t="str">
-        <v>Selected</v>
+        <v>Thank you</v>
       </c>
       <c r="O5" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 5 pm coming"</v>
+        <v>Auto-scheduled via WhatsApp AI: "Me kal interview Dene a nhi ska tha to kya mera interview resedule kr skte ho"</v>
       </c>
     </row>
   </sheetData>

--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -645,7 +645,7 @@
         <v>20-Aug-2026, 2:12 pm</v>
       </c>
       <c r="N5" t="str">
-        <v>Thank you</v>
+        <v>manisha meena.pdf</v>
       </c>
       <c r="O5" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Me kal interview Dene a nhi ska tha to kya mera interview resedule kr skte ho"</v>

--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -627,7 +627,7 @@
         <v>Interview Scheduled</v>
       </c>
       <c r="H5" t="str">
-        <v>22-Aug-2026, 11:00 am</v>
+        <v>21-Aug-2026, 1:00 pm</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -645,10 +645,10 @@
         <v>20-Aug-2026, 2:12 pm</v>
       </c>
       <c r="N5" t="str">
-        <v>manisha meena.pdf</v>
+        <v>Apply</v>
       </c>
       <c r="O5" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Me kal interview Dene a nhi ska tha to kya mera interview resedule kr skte ho"</v>
+        <v>Auto-scheduled via WhatsApp AI: "Arjun_Meena Backen Resume (1).pdf"</v>
       </c>
     </row>
   </sheetData>

--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O64"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -468,25 +468,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Mohit 🎬</v>
+        <v>Candidate</v>
       </c>
       <c r="C2" t="str">
-        <v>+917470584339</v>
+        <v>+172146936524879</v>
       </c>
       <c r="D2" t="str">
-        <v>Video Editor</v>
+        <v>General Applicant</v>
       </c>
       <c r="E2" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>Interview Scheduled</v>
+        <v>Applied</v>
       </c>
       <c r="H2" t="str">
-        <v>21-Aug-2026, 12:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -498,16 +498,16 @@
         <v>NO</v>
       </c>
       <c r="L2" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M2" t="str">
-        <v>20-Aug-2026, 4:31 pm</v>
+        <v>03-Sept-2026, 4:11 pm</v>
       </c>
       <c r="N2" t="str">
-        <v>Thik hai</v>
+        <v/>
       </c>
       <c r="O2" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -515,28 +515,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Candidate</v>
+        <v>Unnat</v>
       </c>
       <c r="C3" t="str">
-        <v>+447974904959</v>
+        <v>+278880866857060</v>
       </c>
       <c r="D3" t="str">
-        <v>General Applicant</v>
+        <v>Video Editor</v>
       </c>
       <c r="E3" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>https://corrra.com/@unnatportfolio</v>
       </c>
       <c r="G3" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="H3" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 4:00 pm</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="J3" t="str">
         <v>Indore</v>
@@ -548,13 +548,13 @@
         <v>NO</v>
       </c>
       <c r="M3" t="str">
-        <v>20-Aug-2026, 4:10 pm</v>
+        <v>03-Sept-2026, 3:58 pm</v>
       </c>
       <c r="N3" t="str">
-        <v>[unsupported message received]</v>
+        <v>4 sep friday</v>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
       </c>
     </row>
     <row r="4">
@@ -562,46 +562,46 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>manisha</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C4" t="str">
-        <v>+917879010084</v>
+        <v>+919329232025</v>
       </c>
       <c r="D4" t="str">
         <v>Video Editor</v>
       </c>
       <c r="E4" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
       </c>
       <c r="G4" t="str">
-        <v>Resume Pending</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="H4" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>Fresher (Paid Internship)</v>
       </c>
       <c r="J4" t="str">
         <v>Indore</v>
       </c>
       <c r="K4" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="L4" t="str">
         <v>NO</v>
       </c>
       <c r="M4" t="str">
-        <v>20-Aug-2026, 3:49 pm</v>
+        <v>03-Sept-2026, 3:35 pm</v>
       </c>
       <c r="N4" t="str">
-        <v>Manual Entry: Role Video Editor, Portfolio: N/A</v>
+        <v>Kal dopahar 2 baje</v>
       </c>
       <c r="O4" t="str">
-        <v/>
+        <v>Test auto schedule</v>
       </c>
     </row>
     <row r="5">
@@ -609,51 +609,2856 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
+        <v>Ritz</v>
+      </c>
+      <c r="C5" t="str">
+        <v>+3908772606086</v>
+      </c>
+      <c r="D5" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E5" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M5" t="str">
+        <v>03-Sept-2026, 3:13 pm</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Hello! Can I get more info on this?</v>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Bhumi</v>
+      </c>
+      <c r="C6" t="str">
+        <v>+29381938409686</v>
+      </c>
+      <c r="D6" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E6" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K6" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L6" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M6" t="str">
+        <v>03-Sept-2026, 3:11 pm</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Abhi</v>
+      </c>
+      <c r="C7" t="str">
+        <v>+87119217348679</v>
+      </c>
+      <c r="D7" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E7" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K7" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L7" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M7" t="str">
+        <v>03-Sept-2026, 3:09 pm</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Hello! Can I get more info on this?</v>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sunshine ✨</v>
+      </c>
+      <c r="C8" t="str">
+        <v>+260910824312929</v>
+      </c>
+      <c r="D8" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E8" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M8" t="str">
+        <v>03-Sept-2026, 2:56 pm</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Hello! Can I get more info on this?</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
         <v>Arjun Meena</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C9" t="str">
+        <v>+114405211672638</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E9" t="str">
+        <v>YES</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="H9" t="str">
+        <v>03-Sept-2026, 5:00 pm</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K9" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L9" t="str">
+        <v>YES</v>
+      </c>
+      <c r="M9" t="str">
+        <v>03-Sept-2026, 2:29 pm</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Yes a rha hun</v>
+      </c>
+      <c r="O9" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Web Developer</v>
+      </c>
+      <c r="C10" t="str">
+        <v>+6537644904640</v>
+      </c>
+      <c r="D10" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E10" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="H10" t="str">
+        <v>03-Sept-2026, 1:00 pm</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M10" t="str">
+        <v>03-Sept-2026, 2:05 pm</v>
+      </c>
+      <c r="N10" t="str" xml:space="preserve">
+        <v xml:space="preserve">We’re hiring for BCT Consulting - SDE 1 (Any Backend - Java or Python) with Strong DSA - Problems solved more than 500.
+Location: Chennai (Preferred only chennai based candidates to apply)
+Immediate Joiners. 
+NIT IIT Based Candidates preferred. 
+Skills Required: Core Java / Advanced Java or Python, Backend development using Spring Boot &amp; Microservices, Strong DSA (Data Structures &amp; Algorithms)
+Experience: 1 - 3 Yrs. with strong DSA
+What You’ll Work On:
+High-scale backend services, Cloud-native applications on AWS, API design &amp; performance optimization, Distributed systems and microservices architecture, Problem-solving
+📍 Location: Chennai
+💼Role: SDE1 
+🎯Preference: Immediate Joiners 
+📩 Interested candidates can DM me or send resumes (Mandatory: with leetcode / geeksforgeeks - profile link) to:</v>
+      </c>
+      <c r="O10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Auto-scheduled via WhatsApp AI: "Dexian India is hiring an experienced Principle Java Engineer (Hyderabad) with strong expertise in:
+🔹 Java / Java EE &amp; Spring Boot
+🔹 Angular 13+ &amp; TypeScript
+🔹 Microservices &amp; REST APIs
+🔹 Kafka &amp; Event-Driven Architecture
+🔹 AWS, Kubernetes &amp; Docker
+🔹 CI/CD – Git, Bitbucket, Maven, Jenkins
+🔹 IBM MQ / Solace &amp; Application Servers
+🔹 JUnit, Mockito, Jasmine &amp; Karma
+🔹 System Design, Design Patterns &amp; Architecture
+📍 Location: [Hyderabad]
+💼 Experience: 10+ Years
+If you're interested, please share your updated resume at  along with the following details:
+• Total relevant experience in Java :
+• Total relavant exp in Angular :
+• Current location : 
+• Official notice period/LWD
+• Current CTC
+• Expected CTC
+Feel free to like, share, or tag someone who might be a great fit."</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>manuuu😎</v>
+      </c>
+      <c r="C11" t="str">
+        <v>+56607786442825</v>
+      </c>
+      <c r="D11" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E11" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K11" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L11" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M11" t="str">
+        <v>03-Sept-2026, 1:45 pm</v>
+      </c>
+      <c r="N11" t="str">
+        <v>Kuchh to</v>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Ultramodern Technologies Pvt Ltd</v>
+      </c>
+      <c r="C12" t="str">
+        <v>+149834547884237</v>
+      </c>
+      <c r="D12" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E12" t="str">
+        <v>YES</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="H12" t="str">
+        <v>04-Sept-2026, 2:00 pm</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K12" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L12" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M12" t="str">
+        <v>03-Sept-2026, 1:35 pm</v>
+      </c>
+      <c r="N12" t="str">
+        <v>[Image received]</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Can you come for interview tomorrow between 2 pm to 4 pm ?"</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>News - Dainik Bhaskar Hindi - India, Rajasthan, Madhya Pradesh, MP, CG, UP, Bihar, Delhi</v>
+      </c>
+      <c r="C13" t="str">
+        <v>+120363171914862438</v>
+      </c>
+      <c r="D13" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E13" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F13" t="str">
+        <v>https://dainik.bhaskar.com/OeMUcjzT75b</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="H13" t="str">
+        <v>03-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K13" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L13" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M13" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N13" t="str" xml:space="preserve">
+        <v xml:space="preserve">*बाइक टैक्सी वालों के लिए बड़ी खबर!* गडकरी ने बताया 8 करोड़ नौकरियों का प्लान, राज्यों से की ये खास अपील 
+*पढ़ें पूरी खबर-*  https://dainik.bhaskar.com/OeMUcjzT75b</v>
+      </c>
+      <c r="O13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Auto-scheduled via WhatsApp AI: "*बाइक टैक्सी वालों के लिए बड़ी खबर!* गडकरी ने बताया 8 करोड़ नौकरियों का प्लान, राज्यों से की ये खास अपील 
+*पढ़ें पूरी खबर-*  https://dainik.bhaskar.com/OeMUcjzT75b"</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C14" t="str">
+        <v>+247038549704930</v>
+      </c>
+      <c r="D14" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E14" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K14" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L14" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M14" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C15" t="str">
+        <v>+230468096139363</v>
+      </c>
+      <c r="D15" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E15" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K15" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L15" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M15" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C16" t="str">
+        <v>+97053392818366</v>
+      </c>
+      <c r="D16" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E16" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K16" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L16" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M16" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C17" t="str">
+        <v>+236047795490957</v>
+      </c>
+      <c r="D17" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E17" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K17" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L17" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M17" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C18" t="str">
+        <v>+131435277099154</v>
+      </c>
+      <c r="D18" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E18" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K18" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L18" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M18" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C19" t="str">
+        <v>+271467753304109</v>
+      </c>
+      <c r="D19" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E19" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K19" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L19" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M19" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C20" t="str">
+        <v>+211905717256387</v>
+      </c>
+      <c r="D20" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E20" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K20" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L20" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M20" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C21" t="str">
+        <v>+46532330012857</v>
+      </c>
+      <c r="D21" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E21" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K21" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L21" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M21" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C22" t="str">
+        <v>+35944598089881</v>
+      </c>
+      <c r="D22" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E22" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K22" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L22" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M22" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C23" t="str">
+        <v>+86342147010597</v>
+      </c>
+      <c r="D23" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E23" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K23" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L23" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M23" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C24" t="str">
+        <v>+174831089791075</v>
+      </c>
+      <c r="D24" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E24" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K24" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L24" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M24" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C25" t="str">
+        <v>+3423726477499</v>
+      </c>
+      <c r="D25" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E25" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K25" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L25" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M25" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C26" t="str">
+        <v>+248429565460671</v>
+      </c>
+      <c r="D26" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E26" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K26" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L26" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M26" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C27" t="str">
+        <v>+242682832109651</v>
+      </c>
+      <c r="D27" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E27" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K27" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L27" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M27" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Rounak Jain</v>
+      </c>
+      <c r="C28" t="str">
+        <v>+156259969937559</v>
+      </c>
+      <c r="D28" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E28" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K28" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L28" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M28" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C29" t="str">
+        <v>+31830707306550</v>
+      </c>
+      <c r="D29" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E29" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K29" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L29" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M29" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C30" t="str">
+        <v>+240136520491067</v>
+      </c>
+      <c r="D30" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E30" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K30" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L30" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M30" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C31" t="str">
+        <v>+154876537499735</v>
+      </c>
+      <c r="D31" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E31" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K31" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L31" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M31" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C32" t="str">
+        <v>+275020412678313</v>
+      </c>
+      <c r="D32" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E32" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K32" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L32" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M32" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C33" t="str">
+        <v>+269166338678802</v>
+      </c>
+      <c r="D33" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E33" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K33" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L33" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M33" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C34" t="str">
+        <v>+129325911289876</v>
+      </c>
+      <c r="D34" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E34" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K34" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L34" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M34" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C35" t="str">
+        <v>+252604374368294</v>
+      </c>
+      <c r="D35" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E35" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K35" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L35" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M35" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C36" t="str">
+        <v>+126259891798031</v>
+      </c>
+      <c r="D36" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E36" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K36" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L36" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M36" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C37" t="str">
+        <v>+161109206159561</v>
+      </c>
+      <c r="D37" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E37" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K37" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L37" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M37" t="str">
+        <v>03-Sept-2026, 1:31 pm</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C38" t="str">
+        <v>+200537005932777</v>
+      </c>
+      <c r="D38" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E38" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K38" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L38" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M38" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C39" t="str">
+        <v>+194776834031826</v>
+      </c>
+      <c r="D39" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E39" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K39" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L39" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M39" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C40" t="str">
+        <v>+131787112071348</v>
+      </c>
+      <c r="D40" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E40" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K40" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L40" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M40" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C41" t="str">
+        <v>+67121799274566</v>
+      </c>
+      <c r="D41" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E41" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K41" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L41" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M41" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C42" t="str">
+        <v>+6687884861548</v>
+      </c>
+      <c r="D42" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E42" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K42" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L42" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M42" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C43" t="str">
+        <v>+279422234030258</v>
+      </c>
+      <c r="D43" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E43" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K43" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L43" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M43" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C44" t="str">
+        <v>+258801978630262</v>
+      </c>
+      <c r="D44" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E44" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K44" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L44" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M44" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C45" t="str">
+        <v>+55448145281236</v>
+      </c>
+      <c r="D45" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E45" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K45" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L45" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M45" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C46" t="str">
+        <v>+172271440277626</v>
+      </c>
+      <c r="D46" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E46" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K46" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L46" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M46" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C47" t="str">
+        <v>+251634282189028</v>
+      </c>
+      <c r="D47" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E47" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K47" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L47" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M47" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C48" t="str">
+        <v>+124618627125375</v>
+      </c>
+      <c r="D48" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E48" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K48" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L48" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M48" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C49" t="str">
+        <v>+19679691202720</v>
+      </c>
+      <c r="D49" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E49" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K49" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L49" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M49" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C50" t="str">
+        <v>+182115253641387</v>
+      </c>
+      <c r="D50" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E50" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K50" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L50" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M50" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Viney Dubey HR</v>
+      </c>
+      <c r="C51" t="str">
+        <v>+18237035155664</v>
+      </c>
+      <c r="D51" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E51" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K51" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L51" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M51" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N51" t="str">
+        <v>Current salary</v>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C52" t="str">
+        <v>+179564479275212</v>
+      </c>
+      <c r="D52" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E52" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K52" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L52" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M52" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C53" t="str">
+        <v>+206992442433648</v>
+      </c>
+      <c r="D53" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E53" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K53" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L53" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M53" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C54" t="str">
+        <v>+245728450482244</v>
+      </c>
+      <c r="D54" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E54" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K54" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L54" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M54" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Rahul Indore</v>
+      </c>
+      <c r="C55" t="str">
+        <v>+22922374717547</v>
+      </c>
+      <c r="D55" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E55" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K55" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L55" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M55" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C56" t="str">
+        <v>+45995190685883</v>
+      </c>
+      <c r="D56" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E56" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K56" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L56" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M56" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C57" t="str">
+        <v>+172979891732506</v>
+      </c>
+      <c r="D57" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E57" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K57" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L57" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M57" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C58" t="str">
+        <v>+33166609928222</v>
+      </c>
+      <c r="D58" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E58" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K58" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L58" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M58" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C59" t="str">
+        <v>+188102706462973</v>
+      </c>
+      <c r="D59" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E59" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K59" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L59" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M59" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Priyanshu</v>
+      </c>
+      <c r="C60" t="str">
+        <v>+18571606401272</v>
+      </c>
+      <c r="D60" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E60" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K60" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L60" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M60" t="str">
+        <v>03-Sept-2026, 1:30 pm</v>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Mohit 🎬</v>
+      </c>
+      <c r="C61" t="str">
+        <v>+917470584339</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E61" t="str">
+        <v>YES</v>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="H61" t="str">
+        <v>21-Aug-2026, 12:00 pm</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K61" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L61" t="str">
+        <v>YES</v>
+      </c>
+      <c r="M61" t="str">
+        <v>20-Aug-2026, 4:31 pm</v>
+      </c>
+      <c r="N61" t="str">
+        <v>Thik hai</v>
+      </c>
+      <c r="O61" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C62" t="str">
+        <v>+447974904959</v>
+      </c>
+      <c r="D62" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E62" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K62" t="str">
+        <v>YES</v>
+      </c>
+      <c r="L62" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M62" t="str">
+        <v>20-Aug-2026, 4:10 pm</v>
+      </c>
+      <c r="N62" t="str">
+        <v>[unsupported message received]</v>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>manisha</v>
+      </c>
+      <c r="C63" t="str">
+        <v>+917879010084</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E63" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K63" t="str">
+        <v>YES</v>
+      </c>
+      <c r="L63" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M63" t="str">
+        <v>20-Aug-2026, 3:49 pm</v>
+      </c>
+      <c r="N63" t="str">
+        <v>Manual Entry: Role Video Editor, Portfolio: N/A</v>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Arjun Meena</v>
+      </c>
+      <c r="C64" t="str">
         <v>+918357977322</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D64" t="str">
         <v>Video Editor</v>
       </c>
-      <c r="E5" t="str">
+      <c r="E64" t="str">
         <v>YES</v>
       </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
         <v>Interview Scheduled</v>
       </c>
-      <c r="H5" t="str">
+      <c r="H64" t="str">
         <v>21-Aug-2026, 1:00 pm</v>
       </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="K5" t="str">
-        <v>NO</v>
-      </c>
-      <c r="L5" t="str">
-        <v>NO</v>
-      </c>
-      <c r="M5" t="str">
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K64" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L64" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M64" t="str">
         <v>20-Aug-2026, 2:12 pm</v>
       </c>
-      <c r="N5" t="str">
+      <c r="N64" t="str">
         <v>Apply</v>
       </c>
-      <c r="O5" t="str">
+      <c r="O64" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Arjun_Meena Backen Resume (1).pdf"</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O64"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O66"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -468,10 +468,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Candidate</v>
+        <v>Nancy Ajmera</v>
       </c>
       <c r="C2" t="str">
-        <v>+172146936524879</v>
+        <v>+38899686625461</v>
       </c>
       <c r="D2" t="str">
         <v>General Applicant</v>
@@ -501,10 +501,10 @@
         <v>NO</v>
       </c>
       <c r="M2" t="str">
-        <v>03-Sept-2026, 4:11 pm</v>
+        <v>03-Sept-2026, 5:03 pm</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>Hello! Can I get more info on this?</v>
       </c>
       <c r="O2" t="str">
         <v/>
@@ -515,28 +515,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Unnat</v>
+        <v>Candidate</v>
       </c>
       <c r="C3" t="str">
-        <v>+278880866857060</v>
+        <v>+28721134207059</v>
       </c>
       <c r="D3" t="str">
-        <v>Video Editor</v>
+        <v>General Applicant</v>
       </c>
       <c r="E3" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="F3" t="str">
-        <v>https://corrra.com/@unnatportfolio</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>Interview Scheduled</v>
+        <v>Applied</v>
       </c>
       <c r="H3" t="str">
-        <v>04-Sept-2026, 4:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="I3" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v/>
       </c>
       <c r="J3" t="str">
         <v>Indore</v>
@@ -548,13 +548,13 @@
         <v>NO</v>
       </c>
       <c r="M3" t="str">
-        <v>03-Sept-2026, 3:58 pm</v>
+        <v>03-Sept-2026, 5:00 pm</v>
       </c>
       <c r="N3" t="str">
-        <v>4 sep friday</v>
+        <v>Hello! Can I get more info on this?</v>
       </c>
       <c r="O3" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -562,28 +562,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Arjun Meena</v>
+        <v>Candidate</v>
       </c>
       <c r="C4" t="str">
-        <v>+919329232025</v>
+        <v>+172146936524879</v>
       </c>
       <c r="D4" t="str">
-        <v>Video Editor</v>
+        <v>General Applicant</v>
       </c>
       <c r="E4" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="F4" t="str">
-        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>Interview Scheduled</v>
+        <v>Applied</v>
       </c>
       <c r="H4" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="I4" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v/>
       </c>
       <c r="J4" t="str">
         <v>Indore</v>
@@ -595,13 +595,13 @@
         <v>NO</v>
       </c>
       <c r="M4" t="str">
-        <v>03-Sept-2026, 3:35 pm</v>
+        <v>03-Sept-2026, 4:11 pm</v>
       </c>
       <c r="N4" t="str">
-        <v>Kal dopahar 2 baje</v>
+        <v/>
       </c>
       <c r="O4" t="str">
-        <v>Test auto schedule</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -609,28 +609,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Ritz</v>
+        <v>Unnat</v>
       </c>
       <c r="C5" t="str">
-        <v>+3908772606086</v>
+        <v>+278880866857060</v>
       </c>
       <c r="D5" t="str">
-        <v>General Applicant</v>
+        <v>Video Editor</v>
       </c>
       <c r="E5" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>https://corrra.com/@unnatportfolio</v>
       </c>
       <c r="G5" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="H5" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 4:00 pm</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="J5" t="str">
         <v>Indore</v>
@@ -642,13 +642,13 @@
         <v>NO</v>
       </c>
       <c r="M5" t="str">
-        <v>03-Sept-2026, 3:13 pm</v>
+        <v>03-Sept-2026, 3:58 pm</v>
       </c>
       <c r="N5" t="str">
-        <v>Hello! Can I get more info on this?</v>
+        <v>4 sep friday</v>
       </c>
       <c r="O5" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
       </c>
     </row>
     <row r="6">
@@ -656,28 +656,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Bhumi</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C6" t="str">
-        <v>+29381938409686</v>
+        <v>+919329232025</v>
       </c>
       <c r="D6" t="str">
-        <v>General Applicant</v>
+        <v>Video Editor</v>
       </c>
       <c r="E6" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
       </c>
       <c r="G6" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="H6" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>Fresher (Paid Internship)</v>
       </c>
       <c r="J6" t="str">
         <v>Indore</v>
@@ -689,13 +689,13 @@
         <v>NO</v>
       </c>
       <c r="M6" t="str">
-        <v>03-Sept-2026, 3:11 pm</v>
+        <v>03-Sept-2026, 3:35 pm</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>Kal dopahar 2 baje</v>
       </c>
       <c r="O6" t="str">
-        <v/>
+        <v>Test auto schedule</v>
       </c>
     </row>
     <row r="7">
@@ -703,10 +703,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Abhi</v>
+        <v>Ritz</v>
       </c>
       <c r="C7" t="str">
-        <v>+87119217348679</v>
+        <v>+3908772606086</v>
       </c>
       <c r="D7" t="str">
         <v>General Applicant</v>
@@ -736,7 +736,7 @@
         <v>NO</v>
       </c>
       <c r="M7" t="str">
-        <v>03-Sept-2026, 3:09 pm</v>
+        <v>03-Sept-2026, 3:13 pm</v>
       </c>
       <c r="N7" t="str">
         <v>Hello! Can I get more info on this?</v>
@@ -750,10 +750,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Sunshine ✨</v>
+        <v>Bhumi</v>
       </c>
       <c r="C8" t="str">
-        <v>+260910824312929</v>
+        <v>+29381938409686</v>
       </c>
       <c r="D8" t="str">
         <v>General Applicant</v>
@@ -783,10 +783,10 @@
         <v>NO</v>
       </c>
       <c r="M8" t="str">
-        <v>03-Sept-2026, 2:56 pm</v>
+        <v>03-Sept-2026, 3:11 pm</v>
       </c>
       <c r="N8" t="str">
-        <v>Hello! Can I get more info on this?</v>
+        <v/>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -797,28 +797,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Arjun Meena</v>
+        <v>Abhi</v>
       </c>
       <c r="C9" t="str">
-        <v>+114405211672638</v>
+        <v>+87119217348679</v>
       </c>
       <c r="D9" t="str">
-        <v>Video Editor</v>
+        <v>General Applicant</v>
       </c>
       <c r="E9" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>Interview Scheduled</v>
+        <v>Applied</v>
       </c>
       <c r="H9" t="str">
-        <v>03-Sept-2026, 5:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="I9" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v/>
       </c>
       <c r="J9" t="str">
         <v>Indore</v>
@@ -827,59 +827,153 @@
         <v>NO</v>
       </c>
       <c r="L9" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M9" t="str">
-        <v>03-Sept-2026, 2:29 pm</v>
+        <v>03-Sept-2026, 3:09 pm</v>
       </c>
       <c r="N9" t="str">
-        <v>Yes a rha hun</v>
+        <v>Hello! Can I get more info on this?</v>
       </c>
       <c r="O9" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="str">
+        <v>Sunshine ✨</v>
+      </c>
+      <c r="C10" t="str">
+        <v>+260910824312929</v>
+      </c>
+      <c r="D10" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E10" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M10" t="str">
+        <v>03-Sept-2026, 2:56 pm</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Hello! Can I get more info on this?</v>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Arjun Meena</v>
+      </c>
+      <c r="C11" t="str">
+        <v>+114405211672638</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="H11" t="str">
+        <v>03-Sept-2026, 5:00 pm</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K11" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="M11" t="str">
+        <v>03-Sept-2026, 2:29 pm</v>
+      </c>
+      <c r="N11" t="str">
+        <v>Hiiii</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
         <v>Web Developer</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C12" t="str">
         <v>+6537644904640</v>
       </c>
-      <c r="D10" t="str">
-        <v>General Applicant</v>
-      </c>
-      <c r="E10" t="str">
-        <v>PENDING</v>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
+      <c r="D12" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E12" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
         <v>Interview Scheduled</v>
       </c>
-      <c r="H10" t="str">
+      <c r="H12" t="str">
         <v>03-Sept-2026, 1:00 pm</v>
       </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="K10" t="str">
-        <v>NO</v>
-      </c>
-      <c r="L10" t="str">
-        <v>NO</v>
-      </c>
-      <c r="M10" t="str">
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K12" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L12" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M12" t="str">
         <v>03-Sept-2026, 2:05 pm</v>
       </c>
-      <c r="N10" t="str" xml:space="preserve">
+      <c r="N12" t="str" xml:space="preserve">
         <v xml:space="preserve">We’re hiring for BCT Consulting - SDE 1 (Any Backend - Java or Python) with Strong DSA - Problems solved more than 500.
 Location: Chennai (Preferred only chennai based candidates to apply)
 Immediate Joiners. 
@@ -893,7 +987,7 @@
 🎯Preference: Immediate Joiners 
 📩 Interested candidates can DM me or send resumes (Mandatory: with leetcode / geeksforgeeks - profile link) to:</v>
       </c>
-      <c r="O10" t="str" xml:space="preserve">
+      <c r="O12" t="str" xml:space="preserve">
         <v xml:space="preserve">Auto-scheduled via WhatsApp AI: "Dexian India is hiring an experienced Principle Java Engineer (Hyderabad) with strong expertise in:
 🔹 Java / Java EE &amp; Spring Boot
 🔹 Angular 13+ &amp; TypeScript
@@ -916,109 +1010,15 @@
 Feel free to like, share, or tag someone who might be a great fit."</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>manuuu😎</v>
-      </c>
-      <c r="C11" t="str">
-        <v>+56607786442825</v>
-      </c>
-      <c r="D11" t="str">
-        <v>General Applicant</v>
-      </c>
-      <c r="E11" t="str">
-        <v>PENDING</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v>Applied</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="K11" t="str">
-        <v>NO</v>
-      </c>
-      <c r="L11" t="str">
-        <v>NO</v>
-      </c>
-      <c r="M11" t="str">
-        <v>03-Sept-2026, 1:45 pm</v>
-      </c>
-      <c r="N11" t="str">
-        <v>Kuchh to</v>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Ultramodern Technologies Pvt Ltd</v>
-      </c>
-      <c r="C12" t="str">
-        <v>+149834547884237</v>
-      </c>
-      <c r="D12" t="str">
-        <v>General Applicant</v>
-      </c>
-      <c r="E12" t="str">
-        <v>YES</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v>Interview Scheduled</v>
-      </c>
-      <c r="H12" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="K12" t="str">
-        <v>NO</v>
-      </c>
-      <c r="L12" t="str">
-        <v>NO</v>
-      </c>
-      <c r="M12" t="str">
-        <v>03-Sept-2026, 1:35 pm</v>
-      </c>
-      <c r="N12" t="str">
-        <v>[Image received]</v>
-      </c>
-      <c r="O12" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Can you come for interview tomorrow between 2 pm to 4 pm ?"</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>News - Dainik Bhaskar Hindi - India, Rajasthan, Madhya Pradesh, MP, CG, UP, Bihar, Delhi</v>
+        <v>manuuu😎</v>
       </c>
       <c r="C13" t="str">
-        <v>+120363171914862438</v>
+        <v>+56607786442825</v>
       </c>
       <c r="D13" t="str">
         <v>General Applicant</v>
@@ -1027,13 +1027,13 @@
         <v>PENDING</v>
       </c>
       <c r="F13" t="str">
-        <v>https://dainik.bhaskar.com/OeMUcjzT75b</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>Interview Scheduled</v>
+        <v>Applied</v>
       </c>
       <c r="H13" t="str">
-        <v>03-Sept-2026, 11:00 am</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -1048,15 +1048,13 @@
         <v>NO</v>
       </c>
       <c r="M13" t="str">
-        <v>03-Sept-2026, 1:31 pm</v>
-      </c>
-      <c r="N13" t="str" xml:space="preserve">
-        <v xml:space="preserve">*बाइक टैक्सी वालों के लिए बड़ी खबर!* गडकरी ने बताया 8 करोड़ नौकरियों का प्लान, राज्यों से की ये खास अपील 
-*पढ़ें पूरी खबर-*  https://dainik.bhaskar.com/OeMUcjzT75b</v>
-      </c>
-      <c r="O13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Auto-scheduled via WhatsApp AI: "*बाइक टैक्सी वालों के लिए बड़ी खबर!* गडकरी ने बताया 8 करोड़ नौकरियों का प्लान, राज्यों से की ये खास अपील 
-*पढ़ें पूरी खबर-*  https://dainik.bhaskar.com/OeMUcjzT75b"</v>
+        <v>03-Sept-2026, 1:45 pm</v>
+      </c>
+      <c r="N13" t="str">
+        <v>Kuchh to</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1064,25 +1062,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Candidate</v>
+        <v>Ultramodern Technologies Pvt Ltd</v>
       </c>
       <c r="C14" t="str">
-        <v>+247038549704930</v>
+        <v>+149834547884237</v>
       </c>
       <c r="D14" t="str">
         <v>General Applicant</v>
       </c>
       <c r="E14" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="F14" t="str">
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="H14" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -1097,24 +1095,24 @@
         <v>NO</v>
       </c>
       <c r="M14" t="str">
-        <v>03-Sept-2026, 1:31 pm</v>
+        <v>03-Sept-2026, 1:35 pm</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>[Image received]</v>
       </c>
       <c r="O14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
+        <v>Auto-scheduled via WhatsApp AI: "Can you come for interview tomorrow between 2 pm to 4 pm ?"</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Candidate</v>
+        <v>News - Dainik Bhaskar Hindi - India, Rajasthan, Madhya Pradesh, MP, CG, UP, Bihar, Delhi</v>
       </c>
       <c r="C15" t="str">
-        <v>+230468096139363</v>
+        <v>+120363171914862438</v>
       </c>
       <c r="D15" t="str">
         <v>General Applicant</v>
@@ -1123,13 +1121,13 @@
         <v>PENDING</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>https://dainik.bhaskar.com/OeMUcjzT75b</v>
       </c>
       <c r="G15" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="H15" t="str">
-        <v>Not Scheduled</v>
+        <v>03-Sept-2026, 11:00 am</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -1146,11 +1144,13 @@
       <c r="M15" t="str">
         <v>03-Sept-2026, 1:31 pm</v>
       </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
+      <c r="N15" t="str" xml:space="preserve">
+        <v xml:space="preserve">*बाइक टैक्सी वालों के लिए बड़ी खबर!* गडकरी ने बताया 8 करोड़ नौकरियों का प्लान, राज्यों से की ये खास अपील 
+*पढ़ें पूरी खबर-*  https://dainik.bhaskar.com/OeMUcjzT75b</v>
+      </c>
+      <c r="O15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Auto-scheduled via WhatsApp AI: "*बाइक टैक्सी वालों के लिए बड़ी खबर!* गडकरी ने बताया 8 करोड़ नौकरियों का प्लान, राज्यों से की ये खास अपील 
+*पढ़ें पूरी खबर-*  https://dainik.bhaskar.com/OeMUcjzT75b"</v>
       </c>
     </row>
     <row r="16">
@@ -1161,7 +1161,7 @@
         <v>Candidate</v>
       </c>
       <c r="C16" t="str">
-        <v>+97053392818366</v>
+        <v>+247038549704930</v>
       </c>
       <c r="D16" t="str">
         <v>General Applicant</v>
@@ -1208,7 +1208,7 @@
         <v>Candidate</v>
       </c>
       <c r="C17" t="str">
-        <v>+236047795490957</v>
+        <v>+230468096139363</v>
       </c>
       <c r="D17" t="str">
         <v>General Applicant</v>
@@ -1255,7 +1255,7 @@
         <v>Candidate</v>
       </c>
       <c r="C18" t="str">
-        <v>+131435277099154</v>
+        <v>+97053392818366</v>
       </c>
       <c r="D18" t="str">
         <v>General Applicant</v>
@@ -1302,7 +1302,7 @@
         <v>Candidate</v>
       </c>
       <c r="C19" t="str">
-        <v>+271467753304109</v>
+        <v>+236047795490957</v>
       </c>
       <c r="D19" t="str">
         <v>General Applicant</v>
@@ -1349,7 +1349,7 @@
         <v>Candidate</v>
       </c>
       <c r="C20" t="str">
-        <v>+211905717256387</v>
+        <v>+131435277099154</v>
       </c>
       <c r="D20" t="str">
         <v>General Applicant</v>
@@ -1396,7 +1396,7 @@
         <v>Candidate</v>
       </c>
       <c r="C21" t="str">
-        <v>+46532330012857</v>
+        <v>+271467753304109</v>
       </c>
       <c r="D21" t="str">
         <v>General Applicant</v>
@@ -1443,7 +1443,7 @@
         <v>Candidate</v>
       </c>
       <c r="C22" t="str">
-        <v>+35944598089881</v>
+        <v>+211905717256387</v>
       </c>
       <c r="D22" t="str">
         <v>General Applicant</v>
@@ -1490,7 +1490,7 @@
         <v>Candidate</v>
       </c>
       <c r="C23" t="str">
-        <v>+86342147010597</v>
+        <v>+46532330012857</v>
       </c>
       <c r="D23" t="str">
         <v>General Applicant</v>
@@ -1537,7 +1537,7 @@
         <v>Candidate</v>
       </c>
       <c r="C24" t="str">
-        <v>+174831089791075</v>
+        <v>+35944598089881</v>
       </c>
       <c r="D24" t="str">
         <v>General Applicant</v>
@@ -1584,7 +1584,7 @@
         <v>Candidate</v>
       </c>
       <c r="C25" t="str">
-        <v>+3423726477499</v>
+        <v>+86342147010597</v>
       </c>
       <c r="D25" t="str">
         <v>General Applicant</v>
@@ -1631,7 +1631,7 @@
         <v>Candidate</v>
       </c>
       <c r="C26" t="str">
-        <v>+248429565460671</v>
+        <v>+174831089791075</v>
       </c>
       <c r="D26" t="str">
         <v>General Applicant</v>
@@ -1678,7 +1678,7 @@
         <v>Candidate</v>
       </c>
       <c r="C27" t="str">
-        <v>+242682832109651</v>
+        <v>+3423726477499</v>
       </c>
       <c r="D27" t="str">
         <v>General Applicant</v>
@@ -1722,10 +1722,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>Rounak Jain</v>
+        <v>Candidate</v>
       </c>
       <c r="C28" t="str">
-        <v>+156259969937559</v>
+        <v>+248429565460671</v>
       </c>
       <c r="D28" t="str">
         <v>General Applicant</v>
@@ -1772,7 +1772,7 @@
         <v>Candidate</v>
       </c>
       <c r="C29" t="str">
-        <v>+31830707306550</v>
+        <v>+242682832109651</v>
       </c>
       <c r="D29" t="str">
         <v>General Applicant</v>
@@ -1816,10 +1816,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Candidate</v>
+        <v>Rounak Jain</v>
       </c>
       <c r="C30" t="str">
-        <v>+240136520491067</v>
+        <v>+156259969937559</v>
       </c>
       <c r="D30" t="str">
         <v>General Applicant</v>
@@ -1866,7 +1866,7 @@
         <v>Candidate</v>
       </c>
       <c r="C31" t="str">
-        <v>+154876537499735</v>
+        <v>+31830707306550</v>
       </c>
       <c r="D31" t="str">
         <v>General Applicant</v>
@@ -1913,7 +1913,7 @@
         <v>Candidate</v>
       </c>
       <c r="C32" t="str">
-        <v>+275020412678313</v>
+        <v>+240136520491067</v>
       </c>
       <c r="D32" t="str">
         <v>General Applicant</v>
@@ -1960,7 +1960,7 @@
         <v>Candidate</v>
       </c>
       <c r="C33" t="str">
-        <v>+269166338678802</v>
+        <v>+154876537499735</v>
       </c>
       <c r="D33" t="str">
         <v>General Applicant</v>
@@ -2007,7 +2007,7 @@
         <v>Candidate</v>
       </c>
       <c r="C34" t="str">
-        <v>+129325911289876</v>
+        <v>+275020412678313</v>
       </c>
       <c r="D34" t="str">
         <v>General Applicant</v>
@@ -2054,7 +2054,7 @@
         <v>Candidate</v>
       </c>
       <c r="C35" t="str">
-        <v>+252604374368294</v>
+        <v>+269166338678802</v>
       </c>
       <c r="D35" t="str">
         <v>General Applicant</v>
@@ -2101,7 +2101,7 @@
         <v>Candidate</v>
       </c>
       <c r="C36" t="str">
-        <v>+126259891798031</v>
+        <v>+129325911289876</v>
       </c>
       <c r="D36" t="str">
         <v>General Applicant</v>
@@ -2148,7 +2148,7 @@
         <v>Candidate</v>
       </c>
       <c r="C37" t="str">
-        <v>+161109206159561</v>
+        <v>+252604374368294</v>
       </c>
       <c r="D37" t="str">
         <v>General Applicant</v>
@@ -2195,7 +2195,7 @@
         <v>Candidate</v>
       </c>
       <c r="C38" t="str">
-        <v>+200537005932777</v>
+        <v>+126259891798031</v>
       </c>
       <c r="D38" t="str">
         <v>General Applicant</v>
@@ -2225,7 +2225,7 @@
         <v>NO</v>
       </c>
       <c r="M38" t="str">
-        <v>03-Sept-2026, 1:30 pm</v>
+        <v>03-Sept-2026, 1:31 pm</v>
       </c>
       <c r="N38" t="str">
         <v/>
@@ -2242,7 +2242,7 @@
         <v>Candidate</v>
       </c>
       <c r="C39" t="str">
-        <v>+194776834031826</v>
+        <v>+161109206159561</v>
       </c>
       <c r="D39" t="str">
         <v>General Applicant</v>
@@ -2272,7 +2272,7 @@
         <v>NO</v>
       </c>
       <c r="M39" t="str">
-        <v>03-Sept-2026, 1:30 pm</v>
+        <v>03-Sept-2026, 1:31 pm</v>
       </c>
       <c r="N39" t="str">
         <v/>
@@ -2289,7 +2289,7 @@
         <v>Candidate</v>
       </c>
       <c r="C40" t="str">
-        <v>+131787112071348</v>
+        <v>+200537005932777</v>
       </c>
       <c r="D40" t="str">
         <v>General Applicant</v>
@@ -2336,7 +2336,7 @@
         <v>Candidate</v>
       </c>
       <c r="C41" t="str">
-        <v>+67121799274566</v>
+        <v>+194776834031826</v>
       </c>
       <c r="D41" t="str">
         <v>General Applicant</v>
@@ -2383,7 +2383,7 @@
         <v>Candidate</v>
       </c>
       <c r="C42" t="str">
-        <v>+6687884861548</v>
+        <v>+131787112071348</v>
       </c>
       <c r="D42" t="str">
         <v>General Applicant</v>
@@ -2430,7 +2430,7 @@
         <v>Candidate</v>
       </c>
       <c r="C43" t="str">
-        <v>+279422234030258</v>
+        <v>+67121799274566</v>
       </c>
       <c r="D43" t="str">
         <v>General Applicant</v>
@@ -2477,7 +2477,7 @@
         <v>Candidate</v>
       </c>
       <c r="C44" t="str">
-        <v>+258801978630262</v>
+        <v>+6687884861548</v>
       </c>
       <c r="D44" t="str">
         <v>General Applicant</v>
@@ -2524,7 +2524,7 @@
         <v>Candidate</v>
       </c>
       <c r="C45" t="str">
-        <v>+55448145281236</v>
+        <v>+279422234030258</v>
       </c>
       <c r="D45" t="str">
         <v>General Applicant</v>
@@ -2571,7 +2571,7 @@
         <v>Candidate</v>
       </c>
       <c r="C46" t="str">
-        <v>+172271440277626</v>
+        <v>+258801978630262</v>
       </c>
       <c r="D46" t="str">
         <v>General Applicant</v>
@@ -2618,7 +2618,7 @@
         <v>Candidate</v>
       </c>
       <c r="C47" t="str">
-        <v>+251634282189028</v>
+        <v>+55448145281236</v>
       </c>
       <c r="D47" t="str">
         <v>General Applicant</v>
@@ -2665,7 +2665,7 @@
         <v>Candidate</v>
       </c>
       <c r="C48" t="str">
-        <v>+124618627125375</v>
+        <v>+172271440277626</v>
       </c>
       <c r="D48" t="str">
         <v>General Applicant</v>
@@ -2712,7 +2712,7 @@
         <v>Candidate</v>
       </c>
       <c r="C49" t="str">
-        <v>+19679691202720</v>
+        <v>+251634282189028</v>
       </c>
       <c r="D49" t="str">
         <v>General Applicant</v>
@@ -2759,7 +2759,7 @@
         <v>Candidate</v>
       </c>
       <c r="C50" t="str">
-        <v>+182115253641387</v>
+        <v>+124618627125375</v>
       </c>
       <c r="D50" t="str">
         <v>General Applicant</v>
@@ -2803,10 +2803,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>Viney Dubey HR</v>
+        <v>Candidate</v>
       </c>
       <c r="C51" t="str">
-        <v>+18237035155664</v>
+        <v>+19679691202720</v>
       </c>
       <c r="D51" t="str">
         <v>General Applicant</v>
@@ -2839,7 +2839,7 @@
         <v>03-Sept-2026, 1:30 pm</v>
       </c>
       <c r="N51" t="str">
-        <v>Current salary</v>
+        <v/>
       </c>
       <c r="O51" t="str">
         <v/>
@@ -2853,7 +2853,7 @@
         <v>Candidate</v>
       </c>
       <c r="C52" t="str">
-        <v>+179564479275212</v>
+        <v>+182115253641387</v>
       </c>
       <c r="D52" t="str">
         <v>General Applicant</v>
@@ -2897,10 +2897,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>Candidate</v>
+        <v>Viney Dubey HR</v>
       </c>
       <c r="C53" t="str">
-        <v>+206992442433648</v>
+        <v>+18237035155664</v>
       </c>
       <c r="D53" t="str">
         <v>General Applicant</v>
@@ -2933,7 +2933,7 @@
         <v>03-Sept-2026, 1:30 pm</v>
       </c>
       <c r="N53" t="str">
-        <v/>
+        <v>Current salary</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Candidate</v>
       </c>
       <c r="C54" t="str">
-        <v>+245728450482244</v>
+        <v>+179564479275212</v>
       </c>
       <c r="D54" t="str">
         <v>General Applicant</v>
@@ -2991,10 +2991,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>Rahul Indore</v>
+        <v>Candidate</v>
       </c>
       <c r="C55" t="str">
-        <v>+22922374717547</v>
+        <v>+206992442433648</v>
       </c>
       <c r="D55" t="str">
         <v>General Applicant</v>
@@ -3041,7 +3041,7 @@
         <v>Candidate</v>
       </c>
       <c r="C56" t="str">
-        <v>+45995190685883</v>
+        <v>+245728450482244</v>
       </c>
       <c r="D56" t="str">
         <v>General Applicant</v>
@@ -3085,10 +3085,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>Candidate</v>
+        <v>Rahul Indore</v>
       </c>
       <c r="C57" t="str">
-        <v>+172979891732506</v>
+        <v>+22922374717547</v>
       </c>
       <c r="D57" t="str">
         <v>General Applicant</v>
@@ -3135,7 +3135,7 @@
         <v>Candidate</v>
       </c>
       <c r="C58" t="str">
-        <v>+33166609928222</v>
+        <v>+45995190685883</v>
       </c>
       <c r="D58" t="str">
         <v>General Applicant</v>
@@ -3182,7 +3182,7 @@
         <v>Candidate</v>
       </c>
       <c r="C59" t="str">
-        <v>+188102706462973</v>
+        <v>+172979891732506</v>
       </c>
       <c r="D59" t="str">
         <v>General Applicant</v>
@@ -3226,10 +3226,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>Priyanshu</v>
+        <v>Candidate</v>
       </c>
       <c r="C60" t="str">
-        <v>+18571606401272</v>
+        <v>+33166609928222</v>
       </c>
       <c r="D60" t="str">
         <v>General Applicant</v>
@@ -3273,25 +3273,25 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>Mohit 🎬</v>
+        <v>Candidate</v>
       </c>
       <c r="C61" t="str">
-        <v>+917470584339</v>
+        <v>+188102706462973</v>
       </c>
       <c r="D61" t="str">
-        <v>Video Editor</v>
+        <v>General Applicant</v>
       </c>
       <c r="E61" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="F61" t="str">
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>Interview Scheduled</v>
+        <v>Applied</v>
       </c>
       <c r="H61" t="str">
-        <v>21-Aug-2026, 12:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -3303,16 +3303,16 @@
         <v>NO</v>
       </c>
       <c r="L61" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M61" t="str">
-        <v>20-Aug-2026, 4:31 pm</v>
+        <v>03-Sept-2026, 1:30 pm</v>
       </c>
       <c r="N61" t="str">
-        <v>Thik hai</v>
+        <v/>
       </c>
       <c r="O61" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -3320,10 +3320,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Candidate</v>
+        <v>Priyanshu</v>
       </c>
       <c r="C62" t="str">
-        <v>+447974904959</v>
+        <v>+18571606401272</v>
       </c>
       <c r="D62" t="str">
         <v>General Applicant</v>
@@ -3335,7 +3335,7 @@
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>Resume Pending</v>
+        <v>Applied</v>
       </c>
       <c r="H62" t="str">
         <v>Not Scheduled</v>
@@ -3347,16 +3347,16 @@
         <v>Indore</v>
       </c>
       <c r="K62" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="L62" t="str">
         <v>NO</v>
       </c>
       <c r="M62" t="str">
-        <v>20-Aug-2026, 4:10 pm</v>
+        <v>03-Sept-2026, 1:30 pm</v>
       </c>
       <c r="N62" t="str">
-        <v>[unsupported message received]</v>
+        <v/>
       </c>
       <c r="O62" t="str">
         <v/>
@@ -3367,25 +3367,25 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>manisha</v>
+        <v>Mohit 🎬</v>
       </c>
       <c r="C63" t="str">
-        <v>+917879010084</v>
+        <v>+917470584339</v>
       </c>
       <c r="D63" t="str">
         <v>Video Editor</v>
       </c>
       <c r="E63" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="F63" t="str">
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>Resume Pending</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="H63" t="str">
-        <v>Not Scheduled</v>
+        <v>21-Aug-2026, 12:00 pm</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -3394,19 +3394,19 @@
         <v>Indore</v>
       </c>
       <c r="K63" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L63" t="str">
         <v>YES</v>
       </c>
-      <c r="L63" t="str">
-        <v>NO</v>
-      </c>
       <c r="M63" t="str">
-        <v>20-Aug-2026, 3:49 pm</v>
+        <v>20-Aug-2026, 4:31 pm</v>
       </c>
       <c r="N63" t="str">
-        <v>Manual Entry: Role Video Editor, Portfolio: N/A</v>
+        <v>Thik hai</v>
       </c>
       <c r="O63" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
       </c>
     </row>
     <row r="64">
@@ -3414,51 +3414,145 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="C64" t="str">
+        <v>+447974904959</v>
+      </c>
+      <c r="D64" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E64" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K64" t="str">
+        <v>YES</v>
+      </c>
+      <c r="L64" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M64" t="str">
+        <v>20-Aug-2026, 4:10 pm</v>
+      </c>
+      <c r="N64" t="str">
+        <v>[unsupported message received]</v>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>manisha</v>
+      </c>
+      <c r="C65" t="str">
+        <v>+917879010084</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E65" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K65" t="str">
+        <v>YES</v>
+      </c>
+      <c r="L65" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M65" t="str">
+        <v>20-Aug-2026, 3:49 pm</v>
+      </c>
+      <c r="N65" t="str">
+        <v>Manual Entry: Role Video Editor, Portfolio: N/A</v>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
         <v>Arjun Meena</v>
       </c>
-      <c r="C64" t="str">
+      <c r="C66" t="str">
         <v>+918357977322</v>
       </c>
-      <c r="D64" t="str">
+      <c r="D66" t="str">
         <v>Video Editor</v>
       </c>
-      <c r="E64" t="str">
+      <c r="E66" t="str">
         <v>YES</v>
       </c>
-      <c r="F64" t="str">
-        <v/>
-      </c>
-      <c r="G64" t="str">
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
         <v>Interview Scheduled</v>
       </c>
-      <c r="H64" t="str">
+      <c r="H66" t="str">
         <v>21-Aug-2026, 1:00 pm</v>
       </c>
-      <c r="I64" t="str">
-        <v/>
-      </c>
-      <c r="J64" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="K64" t="str">
-        <v>NO</v>
-      </c>
-      <c r="L64" t="str">
-        <v>NO</v>
-      </c>
-      <c r="M64" t="str">
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="K66" t="str">
+        <v>NO</v>
+      </c>
+      <c r="L66" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M66" t="str">
         <v>20-Aug-2026, 2:12 pm</v>
       </c>
-      <c r="N64" t="str">
+      <c r="N66" t="str">
         <v>Apply</v>
       </c>
-      <c r="O64" t="str">
+      <c r="O66" t="str">
         <v>Auto-scheduled via WhatsApp AI: "Arjun_Meena Backen Resume (1).pdf"</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O66"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P12"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -430,36 +430,39 @@
         <v>Role Applied</v>
       </c>
       <c r="E1" t="str">
+        <v>Interview Mode</v>
+      </c>
+      <c r="F1" t="str">
         <v>Resume Received</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Portfolio / Drive Link</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Candidate Status</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Interview Date &amp; Time</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Experience</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>City</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Resume Reminder Sent</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Interview 1hr Reminder</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Applied Date</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Last Message</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -468,46 +471,49 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Nancy Ajmera</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C2" t="str">
-        <v>+38899686625461</v>
+        <v>+918357977322</v>
       </c>
       <c r="D2" t="str">
-        <v>General Applicant</v>
+        <v>AI Video Expert</v>
       </c>
       <c r="E2" t="str">
-        <v>PENDING</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>YES</v>
       </c>
       <c r="G2" t="str">
-        <v>Applied</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Not Scheduled</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>07-Sept-2026, 11:00 am</v>
       </c>
       <c r="J2" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="K2" t="str">
         <v>Indore</v>
       </c>
-      <c r="K2" t="str">
-        <v>YES</v>
-      </c>
       <c r="L2" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M2" t="str">
-        <v>03-Sept-2026, 5:03 pm</v>
+        <v>NO</v>
       </c>
       <c r="N2" t="str">
-        <v>Hello! Can I get more info on this?</v>
+        <v>20-Aug-2026, 2:12 pm</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>[Image received]</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Monday morning 11" (In-Person)</v>
       </c>
     </row>
     <row r="3">
@@ -515,93 +521,100 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Unnat</v>
+        <v>Shyama's house of snacks</v>
       </c>
       <c r="C3" t="str">
-        <v>+278880866857060</v>
+        <v>+917693884339</v>
       </c>
       <c r="D3" t="str">
-        <v>Video Editor</v>
+        <v>Digital Marketing Manager</v>
       </c>
       <c r="E3" t="str">
-        <v>YES</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="F3" t="str">
-        <v>https://corrra.com/@unnatportfolio</v>
+        <v>YES</v>
       </c>
       <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>Interview Scheduled</v>
       </c>
-      <c r="H3" t="str">
-        <v>04-Sept-2026, 4:00 pm</v>
-      </c>
       <c r="I3" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v>05-Sept-2026, 11:00 am</v>
       </c>
       <c r="J3" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="K3" t="str">
         <v>Indore</v>
       </c>
-      <c r="K3" t="str">
-        <v>NO</v>
-      </c>
       <c r="L3" t="str">
         <v>NO</v>
       </c>
       <c r="M3" t="str">
-        <v>03-Sept-2026, 3:58 pm</v>
+        <v>NO</v>
       </c>
       <c r="N3" t="str">
-        <v>4 sep friday</v>
+        <v>04-Sept-2026, 2:28 pm</v>
       </c>
       <c r="O3" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>ok sir</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Arjun Meena</v>
+        <v>BrandSetuDigital</v>
       </c>
       <c r="C4" t="str">
-        <v>+919329232025</v>
+        <v>+919669765911</v>
       </c>
       <c r="D4" t="str">
-        <v>Video Editor</v>
+        <v>General Applicant</v>
       </c>
       <c r="E4" t="str">
-        <v>YES</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="F4" t="str">
-        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+        <v>PENDING</v>
       </c>
       <c r="G4" t="str">
-        <v>Interview Scheduled</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>Applied</v>
       </c>
       <c r="I4" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>Indore</v>
       </c>
-      <c r="K4" t="str">
-        <v>NO</v>
-      </c>
       <c r="L4" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M4" t="str">
-        <v>03-Sept-2026, 3:35 pm</v>
+        <v>NO</v>
       </c>
       <c r="N4" t="str">
-        <v>Kal dopahar 2 baje</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Test auto schedule</v>
+        <v>04-Sept-2026, 2:33 pm</v>
+      </c>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Thank you for contacting BrandSetu Digital! 
+Please let us know how we can help you.</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -609,46 +622,49 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Arjun Meena</v>
+        <v>Mohit 🎬</v>
       </c>
       <c r="C5" t="str">
-        <v>+114405211672638</v>
+        <v>+917470584339</v>
       </c>
       <c r="D5" t="str">
         <v>Video Editor</v>
       </c>
       <c r="E5" t="str">
-        <v>YES</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>YES</v>
       </c>
       <c r="G5" t="str">
-        <v>Interview Scheduled</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>03-Sept-2026, 5:00 pm</v>
+        <v>Resume Received</v>
       </c>
       <c r="I5" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
         <v>Indore</v>
       </c>
-      <c r="K5" t="str">
-        <v>NO</v>
-      </c>
       <c r="L5" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M5" t="str">
-        <v>03-Sept-2026, 2:29 pm</v>
+        <v>YES</v>
       </c>
       <c r="N5" t="str">
-        <v>Hiiii</v>
+        <v>20-Aug-2026, 4:31 pm</v>
       </c>
       <c r="O5" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+        <v>Hi!</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
       </c>
     </row>
     <row r="6">
@@ -656,46 +672,49 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Mohit 🎬</v>
+        <v>manshi</v>
       </c>
       <c r="C6" t="str">
-        <v>+917470584339</v>
+        <v>+917828966773</v>
       </c>
       <c r="D6" t="str">
-        <v>Video Editor</v>
+        <v>Digital Marketing Manager</v>
       </c>
       <c r="E6" t="str">
-        <v>YES</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>PENDING</v>
       </c>
       <c r="G6" t="str">
-        <v>Interview Scheduled</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>21-Aug-2026, 12:00 pm</v>
+        <v>Applied</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>Not Scheduled</v>
       </c>
       <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
         <v>Indore</v>
       </c>
-      <c r="K6" t="str">
-        <v>NO</v>
-      </c>
       <c r="L6" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M6" t="str">
-        <v>20-Aug-2026, 4:31 pm</v>
+        <v>NO</v>
       </c>
       <c r="N6" t="str">
-        <v>Thik hai</v>
+        <v>04-Sept-2026, 2:27 pm</v>
       </c>
       <c r="O6" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
+        <v>Manual Entry: Role Digital Marketing Manager, Portfolio: N/A</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -703,46 +722,49 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>manisha</v>
+        <v>Aabid</v>
       </c>
       <c r="C7" t="str">
-        <v>+917879010084</v>
+        <v>+917869724727</v>
       </c>
       <c r="D7" t="str">
-        <v>Video Editor</v>
+        <v>AI Video Expert</v>
       </c>
       <c r="E7" t="str">
-        <v>PENDING</v>
+        <v>In-Person (Indore Office)</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>YES</v>
       </c>
       <c r="G7" t="str">
-        <v>Resume Pending</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Not Scheduled</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="J7" t="str">
+        <v>Experienced (Full-Time)</v>
+      </c>
+      <c r="K7" t="str">
         <v>Indore</v>
       </c>
-      <c r="K7" t="str">
-        <v>YES</v>
-      </c>
       <c r="L7" t="str">
         <v>NO</v>
       </c>
       <c r="M7" t="str">
-        <v>20-Aug-2026, 3:49 pm</v>
+        <v>NO</v>
       </c>
       <c r="N7" t="str">
-        <v>Manual Entry: Role Video Editor, Portfolio: N/A</v>
+        <v>04-Sept-2026, 2:15 pm</v>
       </c>
       <c r="O7" t="str">
-        <v/>
+        <v>Today 2 PM</v>
+      </c>
+      <c r="P7" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
       </c>
     </row>
     <row r="8">
@@ -750,51 +772,254 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
+        <v>Nancy Ajmera</v>
+      </c>
+      <c r="C8" t="str">
+        <v>+38899686625461</v>
+      </c>
+      <c r="D8" t="str">
+        <v>General Applicant</v>
+      </c>
+      <c r="E8" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F8" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>Applied</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L8" t="str">
+        <v>YES</v>
+      </c>
+      <c r="M8" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N8" t="str">
+        <v>03-Sept-2026, 5:03 pm</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Hello! Can I get more info on this?</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Unnat</v>
+      </c>
+      <c r="C9" t="str">
+        <v>+278880866857060</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E9" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F9" t="str">
+        <v>YES</v>
+      </c>
+      <c r="G9" t="str">
+        <v>https://corrra.com/@unnatportfolio</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="I9" t="str">
+        <v>04-Sept-2026, 4:00 pm</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Experienced (Full-Time)</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L9" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M9" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N9" t="str">
+        <v>03-Sept-2026, 3:58 pm</v>
+      </c>
+      <c r="O9" t="str">
+        <v>4 sep friday</v>
+      </c>
+      <c r="P9" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
         <v>Arjun Meena</v>
       </c>
-      <c r="C8" t="str">
-        <v>+918357977322</v>
-      </c>
-      <c r="D8" t="str">
+      <c r="C10" t="str">
+        <v>+919329232025</v>
+      </c>
+      <c r="D10" t="str">
         <v>Video Editor</v>
       </c>
-      <c r="E8" t="str">
-        <v>YES</v>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
+      <c r="E10" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F10" t="str">
+        <v>YES</v>
+      </c>
+      <c r="G10" t="str">
+        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+      </c>
+      <c r="H10" t="str">
         <v>Interview Scheduled</v>
       </c>
-      <c r="H8" t="str">
-        <v>21-Aug-2026, 1:00 pm</v>
-      </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
+      <c r="I10" t="str">
+        <v>04-Sept-2026, 2:00 pm</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="K10" t="str">
         <v>Indore</v>
       </c>
-      <c r="K8" t="str">
-        <v>NO</v>
-      </c>
-      <c r="L8" t="str">
-        <v>NO</v>
-      </c>
-      <c r="M8" t="str">
-        <v>20-Aug-2026, 2:12 pm</v>
-      </c>
-      <c r="N8" t="str">
-        <v>Apply</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Arjun_Meena Backen Resume (1).pdf"</v>
+      <c r="L10" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M10" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N10" t="str">
+        <v>03-Sept-2026, 3:35 pm</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Kal dopahar 2 baje</v>
+      </c>
+      <c r="P10" t="str">
+        <v>Test auto schedule</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Arjun Meena</v>
+      </c>
+      <c r="C11" t="str">
+        <v>+114405211672638</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E11" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="I11" t="str">
+        <v>03-Sept-2026, 5:00 pm</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L11" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M11" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N11" t="str">
+        <v>03-Sept-2026, 2:29 pm</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Hiiii</v>
+      </c>
+      <c r="P11" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>manisha</v>
+      </c>
+      <c r="C12" t="str">
+        <v>+917879010084</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E12" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PENDING</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>Resume Pending</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Not Scheduled</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L12" t="str">
+        <v>YES</v>
+      </c>
+      <c r="M12" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N12" t="str">
+        <v>20-Aug-2026, 3:49 pm</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Manual Entry: Role Video Editor, Portfolio: N/A</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -855,7 +855,7 @@
         <v>NO</v>
       </c>
       <c r="M9" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="N9" t="str">
         <v>03-Sept-2026, 3:58 pm</v>

--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -477,7 +477,7 @@
         <v>+918357977322</v>
       </c>
       <c r="D2" t="str">
-        <v>AI Video Expert</v>
+        <v>Graphic Designer</v>
       </c>
       <c r="E2" t="str">
         <v>In-Person (Indore Office)</v>

--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -589,7 +589,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Applied</v>
+        <v>Resume Pending</v>
       </c>
       <c r="I4" t="str">
         <v>Not Scheduled</v>
@@ -601,7 +601,7 @@
         <v>Indore</v>
       </c>
       <c r="L4" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M4" t="str">
         <v>NO</v>
@@ -690,7 +690,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Applied</v>
+        <v>Resume Pending</v>
       </c>
       <c r="I6" t="str">
         <v>Not Scheduled</v>
@@ -702,7 +702,7 @@
         <v>Indore</v>
       </c>
       <c r="L6" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M6" t="str">
         <v>NO</v>

--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -477,7 +477,7 @@
         <v>+918357977322</v>
       </c>
       <c r="D2" t="str">
-        <v>Graphic Designer</v>
+        <v>SEO &amp; AEO Expert</v>
       </c>
       <c r="E2" t="str">
         <v>In-Person (Indore Office)</v>
@@ -489,31 +489,31 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Received</v>
       </c>
       <c r="I2" t="str">
-        <v>07-Sept-2026, 11:00 am</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J2" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="K2" t="str">
         <v>Indore</v>
       </c>
       <c r="L2" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M2" t="str">
         <v>NO</v>
       </c>
       <c r="N2" t="str">
-        <v>20-Aug-2026, 2:12 pm</v>
+        <v>07-Sept-2026, 1:26 pm</v>
       </c>
       <c r="O2" t="str">
-        <v>[Image received]</v>
+        <v>manisha meena.pdf</v>
       </c>
       <c r="P2" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Monday morning 11" (In-Person)</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -521,10 +521,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Shyama's house of snacks</v>
+        <v>Tanmay Jain</v>
       </c>
       <c r="C3" t="str">
-        <v>+917693884339</v>
+        <v>+919993297342</v>
       </c>
       <c r="D3" t="str">
         <v>Digital Marketing Manager</v>
@@ -539,13 +539,13 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Received</v>
       </c>
       <c r="I3" t="str">
-        <v>05-Sept-2026, 11:00 am</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J3" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>6 years</v>
       </c>
       <c r="K3" t="str">
         <v>Indore</v>
@@ -557,114 +557,114 @@
         <v>NO</v>
       </c>
       <c r="N3" t="str">
-        <v>04-Sept-2026, 2:28 pm</v>
+        <v>07-Sept-2026, 11:48 am</v>
       </c>
       <c r="O3" t="str">
-        <v>ok sir</v>
+        <v>6</v>
       </c>
       <c r="P3" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="str">
+        <v>Shyama's house of snacks</v>
+      </c>
+      <c r="C4" t="str">
+        <v>+917693884339</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Digital Marketing Manager</v>
+      </c>
+      <c r="E4" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F4" t="str">
+        <v>YES</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="I4" t="str">
+        <v>05-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L4" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M4" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N4" t="str">
+        <v>04-Sept-2026, 2:28 pm</v>
+      </c>
+      <c r="O4" t="str">
+        <v>ok sir</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
         <v>BrandSetuDigital</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C5" t="str">
         <v>+919669765911</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D5" t="str">
         <v>General Applicant</v>
       </c>
-      <c r="E4" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="F4" t="str">
+      <c r="E5" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F5" t="str">
         <v>PENDING</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v>Resume Pending</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I5" t="str">
         <v>Not Scheduled</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="L4" t="str">
-        <v>YES</v>
-      </c>
-      <c r="M4" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N4" t="str">
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L5" t="str">
+        <v>YES</v>
+      </c>
+      <c r="M5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N5" t="str">
         <v>04-Sept-2026, 2:33 pm</v>
       </c>
-      <c r="O4" t="str" xml:space="preserve">
+      <c r="O5" t="str" xml:space="preserve">
         <v xml:space="preserve">Thank you for contacting BrandSetu Digital! 
 Please let us know how we can help you.</v>
       </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Mohit 🎬</v>
-      </c>
-      <c r="C5" t="str">
-        <v>+917470584339</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Video Editor</v>
-      </c>
-      <c r="E5" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="F5" t="str">
-        <v>YES</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v>Resume Received</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="L5" t="str">
-        <v>NO</v>
-      </c>
-      <c r="M5" t="str">
-        <v>YES</v>
-      </c>
-      <c r="N5" t="str">
-        <v>20-Aug-2026, 4:31 pm</v>
-      </c>
-      <c r="O5" t="str">
-        <v>Hi!</v>
-      </c>
       <c r="P5" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -672,25 +672,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>manshi</v>
+        <v>Mohit 🎬</v>
       </c>
       <c r="C6" t="str">
-        <v>+917828966773</v>
+        <v>+917470584339</v>
       </c>
       <c r="D6" t="str">
-        <v>Digital Marketing Manager</v>
+        <v>Video Editor</v>
       </c>
       <c r="E6" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F6" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Resume Pending</v>
+        <v>Resume Received</v>
       </c>
       <c r="I6" t="str">
         <v>Not Scheduled</v>
@@ -702,19 +702,19 @@
         <v>Indore</v>
       </c>
       <c r="L6" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M6" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="N6" t="str">
-        <v>04-Sept-2026, 2:27 pm</v>
+        <v>20-Aug-2026, 4:31 pm</v>
       </c>
       <c r="O6" t="str">
-        <v>Manual Entry: Role Digital Marketing Manager, Portfolio: N/A</v>
+        <v>Hi!</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
       </c>
     </row>
     <row r="7">
@@ -722,49 +722,49 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Aabid</v>
+        <v>manshi</v>
       </c>
       <c r="C7" t="str">
-        <v>+917869724727</v>
+        <v>+917828966773</v>
       </c>
       <c r="D7" t="str">
-        <v>AI Video Expert</v>
+        <v>Digital Marketing Manager</v>
       </c>
       <c r="E7" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F7" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Pending</v>
       </c>
       <c r="I7" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J7" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v/>
       </c>
       <c r="K7" t="str">
         <v>Indore</v>
       </c>
       <c r="L7" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M7" t="str">
         <v>NO</v>
       </c>
       <c r="N7" t="str">
-        <v>04-Sept-2026, 2:15 pm</v>
+        <v>04-Sept-2026, 2:27 pm</v>
       </c>
       <c r="O7" t="str">
-        <v>Today 2 PM</v>
+        <v>Manual Entry: Role Digital Marketing Manager, Portfolio: N/A</v>
       </c>
       <c r="P7" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -772,49 +772,49 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Nancy Ajmera</v>
+        <v>Aabid</v>
       </c>
       <c r="C8" t="str">
-        <v>+38899686625461</v>
+        <v>+917869724727</v>
       </c>
       <c r="D8" t="str">
-        <v>General Applicant</v>
+        <v>AI Video Expert</v>
       </c>
       <c r="E8" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F8" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="I8" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="K8" t="str">
         <v>Indore</v>
       </c>
       <c r="L8" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M8" t="str">
         <v>NO</v>
       </c>
       <c r="N8" t="str">
-        <v>03-Sept-2026, 5:03 pm</v>
+        <v>04-Sept-2026, 2:15 pm</v>
       </c>
       <c r="O8" t="str">
-        <v>Hello! Can I get more info on this?</v>
+        <v>Today 2 PM</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
       </c>
     </row>
     <row r="9">
@@ -822,49 +822,49 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Unnat</v>
+        <v>Nancy Ajmera</v>
       </c>
       <c r="C9" t="str">
-        <v>+278880866857060</v>
+        <v>+38899686625461</v>
       </c>
       <c r="D9" t="str">
-        <v>Video Editor</v>
+        <v>General Applicant</v>
       </c>
       <c r="E9" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F9" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="G9" t="str">
-        <v>https://corrra.com/@unnatportfolio</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Interview Scheduled</v>
+        <v>Applied</v>
       </c>
       <c r="I9" t="str">
-        <v>04-Sept-2026, 4:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J9" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v/>
       </c>
       <c r="K9" t="str">
         <v>Indore</v>
       </c>
       <c r="L9" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M9" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="N9" t="str">
-        <v>03-Sept-2026, 3:58 pm</v>
+        <v>03-Sept-2026, 5:03 pm</v>
       </c>
       <c r="O9" t="str">
-        <v>4 sep friday</v>
+        <v>Hello! Can I get more info on this?</v>
       </c>
       <c r="P9" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -872,10 +872,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Arjun Meena</v>
+        <v>Unnat</v>
       </c>
       <c r="C10" t="str">
-        <v>+919329232025</v>
+        <v>+278880866857060</v>
       </c>
       <c r="D10" t="str">
         <v>Video Editor</v>
@@ -887,16 +887,16 @@
         <v>YES</v>
       </c>
       <c r="G10" t="str">
-        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+        <v>https://corrra.com/@unnatportfolio</v>
       </c>
       <c r="H10" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="I10" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>04-Sept-2026, 4:00 pm</v>
       </c>
       <c r="J10" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="K10" t="str">
         <v>Indore</v>
@@ -908,13 +908,13 @@
         <v>YES</v>
       </c>
       <c r="N10" t="str">
-        <v>03-Sept-2026, 3:35 pm</v>
+        <v>03-Sept-2026, 3:58 pm</v>
       </c>
       <c r="O10" t="str">
-        <v>Kal dopahar 2 baje</v>
+        <v>4 sep friday</v>
       </c>
       <c r="P10" t="str">
-        <v>Test auto schedule</v>
+        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
       </c>
     </row>
     <row r="11">
@@ -925,7 +925,7 @@
         <v>Arjun Meena</v>
       </c>
       <c r="C11" t="str">
-        <v>+114405211672638</v>
+        <v>+919329232025</v>
       </c>
       <c r="D11" t="str">
         <v>Video Editor</v>
@@ -937,13 +937,13 @@
         <v>YES</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
       </c>
       <c r="H11" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="I11" t="str">
-        <v>03-Sept-2026, 5:00 pm</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="J11" t="str">
         <v>Fresher (Paid Internship)</v>
@@ -958,13 +958,13 @@
         <v>YES</v>
       </c>
       <c r="N11" t="str">
-        <v>03-Sept-2026, 2:29 pm</v>
+        <v>03-Sept-2026, 3:35 pm</v>
       </c>
       <c r="O11" t="str">
-        <v>Hiiii</v>
+        <v>Kal dopahar 2 baje</v>
       </c>
       <c r="P11" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+        <v>Test auto schedule</v>
       </c>
     </row>
     <row r="12">
@@ -972,10 +972,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>manisha</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C12" t="str">
-        <v>+917879010084</v>
+        <v>+114405211672638</v>
       </c>
       <c r="D12" t="str">
         <v>Video Editor</v>
@@ -984,42 +984,92 @@
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F12" t="str">
+        <v>YES</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="I12" t="str">
+        <v>03-Sept-2026, 5:00 pm</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L12" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M12" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N12" t="str">
+        <v>03-Sept-2026, 2:29 pm</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Hiiii</v>
+      </c>
+      <c r="P12" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>manisha</v>
+      </c>
+      <c r="C13" t="str">
+        <v>+917879010084</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E13" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F13" t="str">
         <v>PENDING</v>
       </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
         <v>Resume Pending</v>
       </c>
-      <c r="I12" t="str">
+      <c r="I13" t="str">
         <v>Not Scheduled</v>
       </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="L12" t="str">
-        <v>YES</v>
-      </c>
-      <c r="M12" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N12" t="str">
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L13" t="str">
+        <v>YES</v>
+      </c>
+      <c r="M13" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N13" t="str">
         <v>20-Aug-2026, 3:49 pm</v>
       </c>
-      <c r="O12" t="str">
+      <c r="O13" t="str">
         <v>Manual Entry: Role Video Editor, Portfolio: N/A</v>
       </c>
-      <c r="P12" t="str">
+      <c r="P13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -471,25 +471,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Arjun Meena</v>
+        <v>Bhumi</v>
       </c>
       <c r="C2" t="str">
-        <v>+918357977322</v>
+        <v>+919302051795</v>
       </c>
       <c r="D2" t="str">
-        <v>SEO &amp; AEO Expert</v>
+        <v>Graphic Designer</v>
       </c>
       <c r="E2" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F2" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Resume Received</v>
+        <v>Applied</v>
       </c>
       <c r="I2" t="str">
         <v>Not Scheduled</v>
@@ -507,10 +507,10 @@
         <v>NO</v>
       </c>
       <c r="N2" t="str">
-        <v>07-Sept-2026, 1:26 pm</v>
+        <v>07-Sept-2026, 2:37 pm</v>
       </c>
       <c r="O2" t="str">
-        <v>manisha meena.pdf</v>
+        <v>Bhoomika Sankhla Resume.PNG</v>
       </c>
       <c r="P2" t="str">
         <v/>
@@ -521,13 +521,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Tanmay Jain</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C3" t="str">
-        <v>+919993297342</v>
+        <v>+918357977322</v>
       </c>
       <c r="D3" t="str">
-        <v>Digital Marketing Manager</v>
+        <v>SEO &amp; AEO Expert</v>
       </c>
       <c r="E3" t="str">
         <v>In-Person (Indore Office)</v>
@@ -539,13 +539,13 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Resume Received</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="I3" t="str">
-        <v>Not Scheduled</v>
+        <v>08-Sept-2026, 11:00 am</v>
       </c>
       <c r="J3" t="str">
-        <v>6 years</v>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="K3" t="str">
         <v>Indore</v>
@@ -557,13 +557,13 @@
         <v>NO</v>
       </c>
       <c r="N3" t="str">
-        <v>07-Sept-2026, 11:48 am</v>
+        <v>07-Sept-2026, 1:26 pm</v>
       </c>
       <c r="O3" t="str">
-        <v>6</v>
+        <v>Hm</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
       </c>
     </row>
     <row r="4">
@@ -571,10 +571,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Shyama's house of snacks</v>
+        <v>Tanmay Jain</v>
       </c>
       <c r="C4" t="str">
-        <v>+917693884339</v>
+        <v>+919993297342</v>
       </c>
       <c r="D4" t="str">
         <v>Digital Marketing Manager</v>
@@ -589,13 +589,13 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Received</v>
       </c>
       <c r="I4" t="str">
-        <v>05-Sept-2026, 11:00 am</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J4" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>6 years</v>
       </c>
       <c r="K4" t="str">
         <v>Indore</v>
@@ -607,114 +607,114 @@
         <v>NO</v>
       </c>
       <c r="N4" t="str">
-        <v>04-Sept-2026, 2:28 pm</v>
+        <v>07-Sept-2026, 11:48 am</v>
       </c>
       <c r="O4" t="str">
-        <v>ok sir</v>
+        <v>6</v>
       </c>
       <c r="P4" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="str">
+        <v>Shyama's house of snacks</v>
+      </c>
+      <c r="C5" t="str">
+        <v>+917693884339</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Digital Marketing Manager</v>
+      </c>
+      <c r="E5" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>YES</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="I5" t="str">
+        <v>05-Sept-2026, 11:00 am</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M5" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N5" t="str">
+        <v>04-Sept-2026, 2:28 pm</v>
+      </c>
+      <c r="O5" t="str">
+        <v>ok sir</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
         <v>BrandSetuDigital</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C6" t="str">
         <v>+919669765911</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D6" t="str">
         <v>General Applicant</v>
       </c>
-      <c r="E5" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="F5" t="str">
+      <c r="E6" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F6" t="str">
         <v>PENDING</v>
       </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>Resume Pending</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I6" t="str">
         <v>Not Scheduled</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="L5" t="str">
-        <v>YES</v>
-      </c>
-      <c r="M5" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N5" t="str">
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L6" t="str">
+        <v>YES</v>
+      </c>
+      <c r="M6" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N6" t="str">
         <v>04-Sept-2026, 2:33 pm</v>
       </c>
-      <c r="O5" t="str" xml:space="preserve">
+      <c r="O6" t="str" xml:space="preserve">
         <v xml:space="preserve">Thank you for contacting BrandSetu Digital! 
 Please let us know how we can help you.</v>
       </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Mohit 🎬</v>
-      </c>
-      <c r="C6" t="str">
-        <v>+917470584339</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Video Editor</v>
-      </c>
-      <c r="E6" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="F6" t="str">
-        <v>YES</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v>Resume Received</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="L6" t="str">
-        <v>NO</v>
-      </c>
-      <c r="M6" t="str">
-        <v>YES</v>
-      </c>
-      <c r="N6" t="str">
-        <v>20-Aug-2026, 4:31 pm</v>
-      </c>
-      <c r="O6" t="str">
-        <v>Hi!</v>
-      </c>
       <c r="P6" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -722,25 +722,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>manshi</v>
+        <v>Mohit 🎬</v>
       </c>
       <c r="C7" t="str">
-        <v>+917828966773</v>
+        <v>+917470584339</v>
       </c>
       <c r="D7" t="str">
-        <v>Digital Marketing Manager</v>
+        <v>Video Editor</v>
       </c>
       <c r="E7" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F7" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Resume Pending</v>
+        <v>Resume Received</v>
       </c>
       <c r="I7" t="str">
         <v>Not Scheduled</v>
@@ -752,19 +752,19 @@
         <v>Indore</v>
       </c>
       <c r="L7" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M7" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="N7" t="str">
-        <v>04-Sept-2026, 2:27 pm</v>
+        <v>20-Aug-2026, 4:31 pm</v>
       </c>
       <c r="O7" t="str">
-        <v>Manual Entry: Role Digital Marketing Manager, Portfolio: N/A</v>
+        <v>Hi!</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
       </c>
     </row>
     <row r="8">
@@ -772,49 +772,49 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Aabid</v>
+        <v>manshi</v>
       </c>
       <c r="C8" t="str">
-        <v>+917869724727</v>
+        <v>+917828966773</v>
       </c>
       <c r="D8" t="str">
-        <v>AI Video Expert</v>
+        <v>Digital Marketing Manager</v>
       </c>
       <c r="E8" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F8" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Pending</v>
       </c>
       <c r="I8" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J8" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v/>
       </c>
       <c r="K8" t="str">
         <v>Indore</v>
       </c>
       <c r="L8" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M8" t="str">
         <v>NO</v>
       </c>
       <c r="N8" t="str">
-        <v>04-Sept-2026, 2:15 pm</v>
+        <v>04-Sept-2026, 2:27 pm</v>
       </c>
       <c r="O8" t="str">
-        <v>Today 2 PM</v>
+        <v>Manual Entry: Role Digital Marketing Manager, Portfolio: N/A</v>
       </c>
       <c r="P8" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -822,49 +822,49 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Nancy Ajmera</v>
+        <v>Aabid</v>
       </c>
       <c r="C9" t="str">
-        <v>+38899686625461</v>
+        <v>+917869724727</v>
       </c>
       <c r="D9" t="str">
-        <v>General Applicant</v>
+        <v>AI Video Expert</v>
       </c>
       <c r="E9" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F9" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="I9" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="K9" t="str">
         <v>Indore</v>
       </c>
       <c r="L9" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M9" t="str">
         <v>NO</v>
       </c>
       <c r="N9" t="str">
-        <v>03-Sept-2026, 5:03 pm</v>
+        <v>04-Sept-2026, 2:15 pm</v>
       </c>
       <c r="O9" t="str">
-        <v>Hello! Can I get more info on this?</v>
+        <v>Today 2 PM</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
       </c>
     </row>
     <row r="10">
@@ -872,49 +872,49 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Unnat</v>
+        <v>Nancy Ajmera</v>
       </c>
       <c r="C10" t="str">
-        <v>+278880866857060</v>
+        <v>+38899686625461</v>
       </c>
       <c r="D10" t="str">
-        <v>Video Editor</v>
+        <v>General Applicant</v>
       </c>
       <c r="E10" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F10" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="G10" t="str">
-        <v>https://corrra.com/@unnatportfolio</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Interview Scheduled</v>
+        <v>Applied</v>
       </c>
       <c r="I10" t="str">
-        <v>04-Sept-2026, 4:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J10" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v/>
       </c>
       <c r="K10" t="str">
         <v>Indore</v>
       </c>
       <c r="L10" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M10" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="N10" t="str">
-        <v>03-Sept-2026, 3:58 pm</v>
+        <v>03-Sept-2026, 5:03 pm</v>
       </c>
       <c r="O10" t="str">
-        <v>4 sep friday</v>
+        <v>Hello! Can I get more info on this?</v>
       </c>
       <c r="P10" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -922,10 +922,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Arjun Meena</v>
+        <v>Unnat</v>
       </c>
       <c r="C11" t="str">
-        <v>+919329232025</v>
+        <v>+278880866857060</v>
       </c>
       <c r="D11" t="str">
         <v>Video Editor</v>
@@ -937,16 +937,16 @@
         <v>YES</v>
       </c>
       <c r="G11" t="str">
-        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+        <v>https://corrra.com/@unnatportfolio</v>
       </c>
       <c r="H11" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="I11" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>04-Sept-2026, 4:00 pm</v>
       </c>
       <c r="J11" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="K11" t="str">
         <v>Indore</v>
@@ -958,13 +958,13 @@
         <v>YES</v>
       </c>
       <c r="N11" t="str">
-        <v>03-Sept-2026, 3:35 pm</v>
+        <v>03-Sept-2026, 3:58 pm</v>
       </c>
       <c r="O11" t="str">
-        <v>Kal dopahar 2 baje</v>
+        <v>4 sep friday</v>
       </c>
       <c r="P11" t="str">
-        <v>Test auto schedule</v>
+        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
       </c>
     </row>
     <row r="12">
@@ -975,7 +975,7 @@
         <v>Arjun Meena</v>
       </c>
       <c r="C12" t="str">
-        <v>+114405211672638</v>
+        <v>+919329232025</v>
       </c>
       <c r="D12" t="str">
         <v>Video Editor</v>
@@ -987,13 +987,13 @@
         <v>YES</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
       </c>
       <c r="H12" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="I12" t="str">
-        <v>03-Sept-2026, 5:00 pm</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="J12" t="str">
         <v>Fresher (Paid Internship)</v>
@@ -1008,13 +1008,13 @@
         <v>YES</v>
       </c>
       <c r="N12" t="str">
-        <v>03-Sept-2026, 2:29 pm</v>
+        <v>03-Sept-2026, 3:35 pm</v>
       </c>
       <c r="O12" t="str">
-        <v>Hiiii</v>
+        <v>Kal dopahar 2 baje</v>
       </c>
       <c r="P12" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+        <v>Test auto schedule</v>
       </c>
     </row>
     <row r="13">
@@ -1022,10 +1022,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>manisha</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C13" t="str">
-        <v>+917879010084</v>
+        <v>+114405211672638</v>
       </c>
       <c r="D13" t="str">
         <v>Video Editor</v>
@@ -1034,42 +1034,92 @@
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F13" t="str">
+        <v>YES</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>Interview Scheduled</v>
+      </c>
+      <c r="I13" t="str">
+        <v>03-Sept-2026, 5:00 pm</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Fresher (Paid Internship)</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L13" t="str">
+        <v>NO</v>
+      </c>
+      <c r="M13" t="str">
+        <v>YES</v>
+      </c>
+      <c r="N13" t="str">
+        <v>03-Sept-2026, 2:29 pm</v>
+      </c>
+      <c r="O13" t="str">
+        <v>Hiiii</v>
+      </c>
+      <c r="P13" t="str">
+        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>manisha</v>
+      </c>
+      <c r="C14" t="str">
+        <v>+917879010084</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Video Editor</v>
+      </c>
+      <c r="E14" t="str">
+        <v>In-Person (Indore Office)</v>
+      </c>
+      <c r="F14" t="str">
         <v>PENDING</v>
       </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
         <v>Resume Pending</v>
       </c>
-      <c r="I13" t="str">
+      <c r="I14" t="str">
         <v>Not Scheduled</v>
       </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="L13" t="str">
-        <v>YES</v>
-      </c>
-      <c r="M13" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N13" t="str">
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="L14" t="str">
+        <v>YES</v>
+      </c>
+      <c r="M14" t="str">
+        <v>NO</v>
+      </c>
+      <c r="N14" t="str">
         <v>20-Aug-2026, 3:49 pm</v>
       </c>
-      <c r="O13" t="str">
+      <c r="O14" t="str">
         <v>Manual Entry: Role Video Editor, Portfolio: N/A</v>
       </c>
-      <c r="P13" t="str">
+      <c r="P14" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/candidates_hiring.xlsx
+++ b/candidates_hiring.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P13"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -471,28 +471,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Bhumi</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C2" t="str">
-        <v>+919302051795</v>
+        <v>+918357977322</v>
       </c>
       <c r="D2" t="str">
-        <v>Graphic Designer</v>
+        <v>SEO &amp; AEO Expert</v>
       </c>
       <c r="E2" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F2" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="I2" t="str">
-        <v>Not Scheduled</v>
+        <v>08-Sept-2026, 11:00 am</v>
       </c>
       <c r="J2" t="str">
         <v>Experienced (Full-Time)</v>
@@ -507,13 +507,13 @@
         <v>NO</v>
       </c>
       <c r="N2" t="str">
-        <v>07-Sept-2026, 2:37 pm</v>
+        <v>07-Sept-2026, 1:26 pm</v>
       </c>
       <c r="O2" t="str">
-        <v>Bhoomika Sankhla Resume.PNG</v>
+        <v>Hm</v>
       </c>
       <c r="P2" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
       </c>
     </row>
     <row r="3">
@@ -521,13 +521,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Arjun Meena</v>
+        <v>Tanmay Jain</v>
       </c>
       <c r="C3" t="str">
-        <v>+918357977322</v>
+        <v>+919993297342</v>
       </c>
       <c r="D3" t="str">
-        <v>SEO &amp; AEO Expert</v>
+        <v>Digital Marketing Manager</v>
       </c>
       <c r="E3" t="str">
         <v>In-Person (Indore Office)</v>
@@ -539,13 +539,13 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Received</v>
       </c>
       <c r="I3" t="str">
-        <v>08-Sept-2026, 11:00 am</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J3" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v>6 years</v>
       </c>
       <c r="K3" t="str">
         <v>Indore</v>
@@ -557,13 +557,13 @@
         <v>NO</v>
       </c>
       <c r="N3" t="str">
-        <v>07-Sept-2026, 1:26 pm</v>
+        <v>07-Sept-2026, 11:48 am</v>
       </c>
       <c r="O3" t="str">
-        <v>Hm</v>
+        <v>6</v>
       </c>
       <c r="P3" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Yes" (In-Person)</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -571,10 +571,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Tanmay Jain</v>
+        <v>Shyama's house of snacks</v>
       </c>
       <c r="C4" t="str">
-        <v>+919993297342</v>
+        <v>+917693884339</v>
       </c>
       <c r="D4" t="str">
         <v>Digital Marketing Manager</v>
@@ -589,13 +589,13 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Resume Received</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="I4" t="str">
-        <v>Not Scheduled</v>
+        <v>05-Sept-2026, 11:00 am</v>
       </c>
       <c r="J4" t="str">
-        <v>6 years</v>
+        <v>Fresher (Paid Internship)</v>
       </c>
       <c r="K4" t="str">
         <v>Indore</v>
@@ -607,89 +607,90 @@
         <v>NO</v>
       </c>
       <c r="N4" t="str">
-        <v>07-Sept-2026, 11:48 am</v>
+        <v>04-Sept-2026, 2:28 pm</v>
       </c>
       <c r="O4" t="str">
-        <v>6</v>
+        <v>ok sir</v>
       </c>
       <c r="P4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
+        <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Shyama's house of snacks</v>
+        <v>BrandSetuDigital</v>
       </c>
       <c r="C5" t="str">
-        <v>+917693884339</v>
+        <v>+919669765911</v>
       </c>
       <c r="D5" t="str">
-        <v>Digital Marketing Manager</v>
+        <v>General Applicant</v>
       </c>
       <c r="E5" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F5" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Pending</v>
       </c>
       <c r="I5" t="str">
-        <v>05-Sept-2026, 11:00 am</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J5" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v/>
       </c>
       <c r="K5" t="str">
         <v>Indore</v>
       </c>
       <c r="L5" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M5" t="str">
         <v>NO</v>
       </c>
       <c r="N5" t="str">
-        <v>04-Sept-2026, 2:28 pm</v>
-      </c>
-      <c r="O5" t="str">
-        <v>ok sir</v>
+        <v>04-Sept-2026, 2:33 pm</v>
+      </c>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Thank you for contacting BrandSetu Digital! 
+Please let us know how we can help you.</v>
       </c>
       <c r="P5" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "ok sir" (In-Person)</v>
-      </c>
-    </row>
-    <row r="6" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>BrandSetuDigital</v>
+        <v>Mohit 🎬</v>
       </c>
       <c r="C6" t="str">
-        <v>+919669765911</v>
+        <v>+917470584339</v>
       </c>
       <c r="D6" t="str">
-        <v>General Applicant</v>
+        <v>Video Editor</v>
       </c>
       <c r="E6" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F6" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Resume Pending</v>
+        <v>Resume Received</v>
       </c>
       <c r="I6" t="str">
         <v>Not Scheduled</v>
@@ -701,20 +702,19 @@
         <v>Indore</v>
       </c>
       <c r="L6" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M6" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="N6" t="str">
-        <v>04-Sept-2026, 2:33 pm</v>
-      </c>
-      <c r="O6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Thank you for contacting BrandSetu Digital! 
-Please let us know how we can help you.</v>
+        <v>20-Aug-2026, 4:31 pm</v>
+      </c>
+      <c r="O6" t="str">
+        <v>Hi!</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
       </c>
     </row>
     <row r="7">
@@ -722,25 +722,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Mohit 🎬</v>
+        <v>manshi</v>
       </c>
       <c r="C7" t="str">
-        <v>+917470584339</v>
+        <v>+917828966773</v>
       </c>
       <c r="D7" t="str">
-        <v>Video Editor</v>
+        <v>Digital Marketing Manager</v>
       </c>
       <c r="E7" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F7" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Resume Received</v>
+        <v>Resume Pending</v>
       </c>
       <c r="I7" t="str">
         <v>Not Scheduled</v>
@@ -752,19 +752,19 @@
         <v>Indore</v>
       </c>
       <c r="L7" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M7" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="N7" t="str">
-        <v>20-Aug-2026, 4:31 pm</v>
+        <v>04-Sept-2026, 2:27 pm</v>
       </c>
       <c r="O7" t="str">
-        <v>Hi!</v>
+        <v>Manual Entry: Role Digital Marketing Manager, Portfolio: N/A</v>
       </c>
       <c r="P7" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Tomorrow morning 12 pm"</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -772,49 +772,49 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>manshi</v>
+        <v>Aabid</v>
       </c>
       <c r="C8" t="str">
-        <v>+917828966773</v>
+        <v>+917869724727</v>
       </c>
       <c r="D8" t="str">
-        <v>Digital Marketing Manager</v>
+        <v>AI Video Expert</v>
       </c>
       <c r="E8" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F8" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Resume Pending</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="I8" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="K8" t="str">
         <v>Indore</v>
       </c>
       <c r="L8" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M8" t="str">
         <v>NO</v>
       </c>
       <c r="N8" t="str">
-        <v>04-Sept-2026, 2:27 pm</v>
+        <v>04-Sept-2026, 2:15 pm</v>
       </c>
       <c r="O8" t="str">
-        <v>Manual Entry: Role Digital Marketing Manager, Portfolio: N/A</v>
+        <v>Today 2 PM</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
       </c>
     </row>
     <row r="9">
@@ -822,49 +822,49 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Aabid</v>
+        <v>Nancy Ajmera</v>
       </c>
       <c r="C9" t="str">
-        <v>+917869724727</v>
+        <v>+38899686625461</v>
       </c>
       <c r="D9" t="str">
-        <v>AI Video Expert</v>
+        <v>General Applicant</v>
       </c>
       <c r="E9" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F9" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Interview Scheduled</v>
+        <v>Applied</v>
       </c>
       <c r="I9" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J9" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v/>
       </c>
       <c r="K9" t="str">
         <v>Indore</v>
       </c>
       <c r="L9" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M9" t="str">
         <v>NO</v>
       </c>
       <c r="N9" t="str">
-        <v>04-Sept-2026, 2:15 pm</v>
+        <v>03-Sept-2026, 5:03 pm</v>
       </c>
       <c r="O9" t="str">
-        <v>Today 2 PM</v>
+        <v>Hello! Can I get more info on this?</v>
       </c>
       <c r="P9" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 2 PM" (In-Person)</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -872,49 +872,49 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Nancy Ajmera</v>
+        <v>Unnat</v>
       </c>
       <c r="C10" t="str">
-        <v>+38899686625461</v>
+        <v>+278880866857060</v>
       </c>
       <c r="D10" t="str">
-        <v>General Applicant</v>
+        <v>Video Editor</v>
       </c>
       <c r="E10" t="str">
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F10" t="str">
-        <v>PENDING</v>
+        <v>YES</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>https://corrra.com/@unnatportfolio</v>
       </c>
       <c r="H10" t="str">
-        <v>Applied</v>
+        <v>Interview Scheduled</v>
       </c>
       <c r="I10" t="str">
-        <v>Not Scheduled</v>
+        <v>04-Sept-2026, 4:00 pm</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>Experienced (Full-Time)</v>
       </c>
       <c r="K10" t="str">
         <v>Indore</v>
       </c>
       <c r="L10" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="M10" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="N10" t="str">
-        <v>03-Sept-2026, 5:03 pm</v>
+        <v>03-Sept-2026, 3:58 pm</v>
       </c>
       <c r="O10" t="str">
-        <v>Hello! Can I get more info on this?</v>
+        <v>4 sep friday</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
       </c>
     </row>
     <row r="11">
@@ -922,10 +922,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Unnat</v>
+        <v>Arjun Meena</v>
       </c>
       <c r="C11" t="str">
-        <v>+278880866857060</v>
+        <v>+919329232025</v>
       </c>
       <c r="D11" t="str">
         <v>Video Editor</v>
@@ -937,16 +937,16 @@
         <v>YES</v>
       </c>
       <c r="G11" t="str">
-        <v>https://corrra.com/@unnatportfolio</v>
+        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
       </c>
       <c r="H11" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="I11" t="str">
-        <v>04-Sept-2026, 4:00 pm</v>
+        <v>04-Sept-2026, 2:00 pm</v>
       </c>
       <c r="J11" t="str">
-        <v>Experienced (Full-Time)</v>
+        <v>Fresher (Paid Internship)</v>
       </c>
       <c r="K11" t="str">
         <v>Indore</v>
@@ -958,13 +958,13 @@
         <v>YES</v>
       </c>
       <c r="N11" t="str">
-        <v>03-Sept-2026, 3:58 pm</v>
+        <v>03-Sept-2026, 3:35 pm</v>
       </c>
       <c r="O11" t="str">
-        <v>4 sep friday</v>
+        <v>Kal dopahar 2 baje</v>
       </c>
       <c r="P11" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "4 sep friday"</v>
+        <v>Test auto schedule</v>
       </c>
     </row>
     <row r="12">
@@ -975,7 +975,7 @@
         <v>Arjun Meena</v>
       </c>
       <c r="C12" t="str">
-        <v>+919329232025</v>
+        <v>+114405211672638</v>
       </c>
       <c r="D12" t="str">
         <v>Video Editor</v>
@@ -987,13 +987,13 @@
         <v>YES</v>
       </c>
       <c r="G12" t="str">
-        <v>https://drive.google.com/drive/folders/sample_portfolio</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v>Interview Scheduled</v>
       </c>
       <c r="I12" t="str">
-        <v>04-Sept-2026, 2:00 pm</v>
+        <v>03-Sept-2026, 5:00 pm</v>
       </c>
       <c r="J12" t="str">
         <v>Fresher (Paid Internship)</v>
@@ -1008,13 +1008,13 @@
         <v>YES</v>
       </c>
       <c r="N12" t="str">
-        <v>03-Sept-2026, 3:35 pm</v>
+        <v>03-Sept-2026, 2:29 pm</v>
       </c>
       <c r="O12" t="str">
-        <v>Kal dopahar 2 baje</v>
+        <v>Hiiii</v>
       </c>
       <c r="P12" t="str">
-        <v>Test auto schedule</v>
+        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
       </c>
     </row>
     <row r="13">
@@ -1022,10 +1022,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Arjun Meena</v>
+        <v>manisha</v>
       </c>
       <c r="C13" t="str">
-        <v>+114405211672638</v>
+        <v>+917879010084</v>
       </c>
       <c r="D13" t="str">
         <v>Video Editor</v>
@@ -1034,92 +1034,42 @@
         <v>In-Person (Indore Office)</v>
       </c>
       <c r="F13" t="str">
-        <v>YES</v>
+        <v>PENDING</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Interview Scheduled</v>
+        <v>Resume Pending</v>
       </c>
       <c r="I13" t="str">
-        <v>03-Sept-2026, 5:00 pm</v>
+        <v>Not Scheduled</v>
       </c>
       <c r="J13" t="str">
-        <v>Fresher (Paid Internship)</v>
+        <v/>
       </c>
       <c r="K13" t="str">
         <v>Indore</v>
       </c>
       <c r="L13" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="M13" t="str">
-        <v>YES</v>
+        <v>NO</v>
       </c>
       <c r="N13" t="str">
-        <v>03-Sept-2026, 2:29 pm</v>
+        <v>20-Aug-2026, 3:49 pm</v>
       </c>
       <c r="O13" t="str">
-        <v>Hiiii</v>
+        <v>Manual Entry: Role Video Editor, Portfolio: N/A</v>
       </c>
       <c r="P13" t="str">
-        <v>Auto-scheduled via WhatsApp AI: "Today 5:3 mint pe mera interview resedule kr do"</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>manisha</v>
-      </c>
-      <c r="C14" t="str">
-        <v>+917879010084</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Video Editor</v>
-      </c>
-      <c r="E14" t="str">
-        <v>In-Person (Indore Office)</v>
-      </c>
-      <c r="F14" t="str">
-        <v>PENDING</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v>Resume Pending</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Not Scheduled</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="L14" t="str">
-        <v>YES</v>
-      </c>
-      <c r="M14" t="str">
-        <v>NO</v>
-      </c>
-      <c r="N14" t="str">
-        <v>20-Aug-2026, 3:49 pm</v>
-      </c>
-      <c r="O14" t="str">
-        <v>Manual Entry: Role Video Editor, Portfolio: N/A</v>
-      </c>
-      <c r="P14" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P13"/>
   </ignoredErrors>
 </worksheet>
 </file>